--- a/Output/BRDM_countarea_ALM_A1_PLCigaretteButts.xlsx
+++ b/Output/BRDM_countarea_ALM_A1_PLCigaretteButts.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,10 +762,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -872,10 +870,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1055,6 +1051,742 @@
       </c>
       <c r="BN3" t="n">
         <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>59.68992248062015</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.23422377080914</v>
+      </c>
+      <c r="E4" t="n">
+        <v>557.5407415334379</v>
+      </c>
+      <c r="F4" t="n">
+        <v>141.3333333333333</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>58.06906272022551</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.69107650503603</v>
+      </c>
+      <c r="J4" t="n">
+        <v>71.32748538011695</v>
+      </c>
+      <c r="K4" t="n">
+        <v>209.8067923033799</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>32.10998877665543</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.789627867986077</v>
+      </c>
+      <c r="O4" t="n">
+        <v>252.8320083053302</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>35.18747290482057</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.282037186211222</v>
+      </c>
+      <c r="T4" t="n">
+        <v>310.296121292376</v>
+      </c>
+      <c r="U4" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>101.5906358937372</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15.20342044358929</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>462.7709209390059</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>185.2745626823169</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.484477169756357</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>38.73008263252166</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.830187728049248</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>159.5323889559204</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>144.3674035501689</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.416699274392295</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>78.27359978522769</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>14.76598641038023</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>230.8982149533232</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>289.757496385131</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>51.88591311029844</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>19.25851267006064</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>286.5285802656326</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>142.531444498526</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>102.8037717832418</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.740646056872627</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>196.4648358801104</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>45.33333333333334</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>87.6918108545749</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>12.37713476832974</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>278.760322388906</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>329.7425474254742</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11.15522783134808</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>302.3255813953488</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>58.66666666666667</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>451.9320389810129</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>9.968266014777642</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>247.3076923076923</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>146.6666666666667</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>13.97767145135566</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>6.621378359791557</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>427.3809523809524</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>31.78294573643411</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17.62485481997677</v>
+      </c>
+      <c r="E5" t="n">
+        <v>93.91015422664844</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>124.6454206144129</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14.8032621916898</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44.72514619883041</v>
+      </c>
+      <c r="K5" t="n">
+        <v>124.7592713036153</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>54.1919191919192</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>126.449471354807</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>45.98585274177479</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.568594085393658</v>
+      </c>
+      <c r="T5" t="n">
+        <v>90.38525384752995</v>
+      </c>
+      <c r="U5" t="n">
+        <v>48</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>186.9921264575069</v>
+      </c>
+      <c r="X5" t="n">
+        <v>35.11437833635615</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>458.708958784237</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>235.2613679817321</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.692047377326565</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>82.76952118415532</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20.21231741792129</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>273.4706226783869</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>282.8608251874793</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.743468140084033</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>65.35705896171011</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>23.81638297034631</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>197.073468332487</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>290.8020004975508</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>32.45298566836215</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>16.45657234993591</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>418.3410083409966</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>140.7463286226835</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.847953216374269</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>99.11951937614388</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.666488318173712</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>133.2455909245886</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>90.47031639466549</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.379660559954061</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>120.5903949877705</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>180.1970415537488</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14.82424929957545</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>267.4347616208082</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>474.7800538432666</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>16.5941982221052</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>224.2521367521367</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>370.6666666666666</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>26.70919723551303</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5.657958381857711</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>218.1547619047619</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>37.33333333333334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>91.47286821705427</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.826945412311266</v>
+      </c>
+      <c r="E6" t="n">
+        <v>139.1031028888607</v>
+      </c>
+      <c r="F6" t="n">
+        <v>48.00000000000001</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>70.1198026779422</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.164327062355087</v>
+      </c>
+      <c r="J6" t="n">
+        <v>79.32163742690058</v>
+      </c>
+      <c r="K6" t="n">
+        <v>172.1696339795337</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>21.31313131313131</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.734677687569478</v>
+      </c>
+      <c r="O6" t="n">
+        <v>273.8767314154578</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>21.66594889463106</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17.61973081915693</v>
+      </c>
+      <c r="T6" t="n">
+        <v>135.9467191787013</v>
+      </c>
+      <c r="U6" t="n">
+        <v>48</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>128.8345955042674</v>
+      </c>
+      <c r="X6" t="n">
+        <v>18.82020539061344</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>330.1827860924851</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>286.8176288966637</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10.7274564127356</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>92.37297164126431</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.891184124918673</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>183.9084878838621</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>105.411095779811</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>65.35538105305547</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>10.2118089473477</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>221.1876875117412</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>335.7412220878263</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>78.0871096146907</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>14.90394391433403</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>358.3821528083587</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>170.3557348579428</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.56947925368978</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>115.475690299992</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.685070163331033</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>114.8340720536425</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>53.33333333333333</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>60.56374288157487</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.449418893863338</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>147.0443271684179</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>239.4450090334236</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10.33482871826604</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>506.5777891359286</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>364.5573746334874</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>9.34335044800161</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>267.5854700854701</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>106.6666666666667</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11.9414946904428</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>36.33492822966507</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>69.73216557992815</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>241.7200854700855</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>50.38759689922481</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.89276035617499</v>
+      </c>
+      <c r="E7" t="n">
+        <v>242.7010806195225</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>73.65176310912744</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16.17838278502523</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.14619883040936</v>
+      </c>
+      <c r="K7" t="n">
+        <v>144.8973925325518</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>54.91582491582491</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.78964552238806</v>
+      </c>
+      <c r="O7" t="n">
+        <v>102.5874928284567</v>
+      </c>
+      <c r="P7" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>74.76994119416678</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9.002392789220055</v>
+      </c>
+      <c r="T7" t="n">
+        <v>89.95577033802994</v>
+      </c>
+      <c r="U7" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="W7" t="n">
+        <v>93.77839884601514</v>
+      </c>
+      <c r="X7" t="n">
+        <v>38.42536070298687</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>413.5813844560571</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>329.4597064748786</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.068376068376068</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16.35338220704074</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.153273826509452</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>208.4756620131288</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>132.002144297267</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.6419753086419753</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>53.85415617973757</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8.407881669740032</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>191.865268687004</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>196.550295051466</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>23.9764718223658</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>14.72967193896584</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>466.5483818707999</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>94.90151521464247</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.923976608187135</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9.409007718628153</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.499476585944588</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>84.13781524760044</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>40.81163691938213</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.402975625197847</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>161.8541234145285</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>259.8803071364047</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>21.50793241547638</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>380.2964477383082</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>382.5357717489881</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.152760676016491</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>223.8888888888889</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.585126430188719</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>52.16267942583732</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>10.20757998487454</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>282.7380952380952</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>101.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,10 +2136,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -1514,10 +2244,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1697,6 +2425,740 @@
       </c>
       <c r="BN3" t="n">
         <v>27.19477073916152</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>28.93249241321166</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.960456159131867</v>
+      </c>
+      <c r="E4" t="n">
+        <v>63.80238646720393</v>
+      </c>
+      <c r="F4" t="n">
+        <v>68.8444300982698</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>26.47869046476983</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.931107651609672</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.27908134006157</v>
+      </c>
+      <c r="K4" t="n">
+        <v>79.42258934285358</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>18.04098439961417</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9466612721441185</v>
+      </c>
+      <c r="O4" t="n">
+        <v>33.69020283035176</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>15.78353122911411</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.897166438041106</v>
+      </c>
+      <c r="T4" t="n">
+        <v>210.8455257089715</v>
+      </c>
+      <c r="U4" t="n">
+        <v>94.9385766342288</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.247219128924647</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.23214855748888</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.35327879580646</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>134.2306253665041</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>94.54038453714578</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.830300159995311</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>20.18503371775786</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.922910473287522</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.892545490904077</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>39.51713999695108</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.585535668753689</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>31.18651256058887</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4.453547875868424</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>30.15239240931828</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>75.05306035488412</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>9.434873031502679</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5.766903717968779</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>62.2864822445837</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>51.1913452937378</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>64.80549820792557</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.159492195927184</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>55.56667813953585</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>30.28751117760146</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>12.48467824757381</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.17357626270378</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>65.53861115499546</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>83.25388579242734</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.071156694774629</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>31.72100600898752</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>201.3179087749515</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.909530203213861</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>18.77767517060149</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>101.8059155670457</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.455444297485866</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>3.842929232585493</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>78.29948798681019</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>18.57118436957883</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>10.42916592796412</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.54147739869128</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.300639939931591</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.988876515698589</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>47.3396864194338</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.406471889373107</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.960269150767447</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28.84799024430701</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>43.38260366771104</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>51.67055537279456</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.79869268479038</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>2.297425970000574</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.161101458125587</v>
+      </c>
+      <c r="T5" t="n">
+        <v>38.43204469766178</v>
+      </c>
+      <c r="U5" t="n">
+        <v>25.85429257288709</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.816496580927726</v>
+      </c>
+      <c r="W5" t="n">
+        <v>29.7773210128509</v>
+      </c>
+      <c r="X5" t="n">
+        <v>20.37074064977535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>205.7333440753951</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>140.9462758368649</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.692047377326565</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.655068736263878</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.333167793874595</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10.59681861660317</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>50.36101027361003</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.7178175272176641</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.294059744817625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>8.020040325385043</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24.18713083247075</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>80.97101670555227</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>10.32966334490729</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3.742405826385232</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.26682115151385</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>50.94062872835056</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.847953216374269</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>28.18371580195035</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.711520192139369</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>25.46099607887701</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>14.60593486680443</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>14.76699393972474</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.97380621313335</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>16.18957437000827</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>56.47676497155387</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.355707383300248</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>130.7910413375846</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>11.62373051610846</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>213.9064384582975</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6.022480422819529</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>23.44122273622109</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>285.9494904893364</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.062732589048379</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.592480680016029</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>64.24182364784257</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>18.57118436957883</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>53.03708056774364</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.915202775397715</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.55388425313217</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.59591794226543</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>14.94458560143526</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.417029812258343</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.02474682306216</v>
+      </c>
+      <c r="K6" t="n">
+        <v>59.68200246986391</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>15.84192974633931</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.220154042834068</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20.29207208811275</v>
+      </c>
+      <c r="P6" t="n">
+        <v>18.85618083164126</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>11.56956848205961</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.20243544234956</v>
+      </c>
+      <c r="T6" t="n">
+        <v>67.00419047098131</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.043106644167024</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.49071198499986</v>
+      </c>
+      <c r="W6" t="n">
+        <v>35.79116041583822</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.10636069862029</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>171.6817128445179</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>136.3883330575926</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.658522674967188</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.446357277691448</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.729136258591351</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>58.03138230394182</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14.44220513862961</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9.173152817885706</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.957015483868525</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>39.05584107876339</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>86.69219087547923</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>23.86761363043862</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.571532223614137</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>93.52828732049664</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>46.36060564050732</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.417693597503085</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>29.44333636372902</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.9179771605354559</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>58.42111063898086</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>26.99794230842212</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>23.53313272875991</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.194856342401376</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>74.69847607003568</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.583937179043478</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>72.3892581478066</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.494093363233792</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>228.5226739571322</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>57.70294298932793</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>175.7274071489852</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.854670731741146</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>48.92057968893381</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>43.61447262345634</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>7.317794615432289</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.719552047616006</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>30.9151700418267</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>23.88489647922335</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>51.91445955715142</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>16.01858784478436</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.178375133572795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.51665740179983</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>19.10755041685444</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.135682679818625</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.596280482464691</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.29914146596887</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>28.91425291221842</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.377838690816529</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.149664848770761</v>
+      </c>
+      <c r="P7" t="n">
+        <v>28.15828277592383</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>14.24153721950005</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.599430222964411</v>
+      </c>
+      <c r="T7" t="n">
+        <v>53.83208609953805</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35.37733109712426</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.260776661041756</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15.41104289220194</v>
+      </c>
+      <c r="X7" t="n">
+        <v>21.82750877503665</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>180.0564876126871</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>156.7073907703099</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.068376068376068</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.804609279998429</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.399050709914331</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25.29109383025586</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>42.01331748513393</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3936123102945644</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17.28943189033507</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3.496496243914745</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>18.0497460851303</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>45.99742204408307</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>12.17329724191455</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5.458010122410601</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>155.7500199762968</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>19.6519203382592</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.923976608187135</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.930793126427494</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.221661694518009</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.345732121348609</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.797958971132712</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>11.86746360324694</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.834672740643632</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>17.2989100043036</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>108.4828168564982</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.883309261923186</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>154.3820575597719</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.988876515698589</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>95.14501739335445</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.07500692232999</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>56.80606492572496</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3.523862797817408</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>20.76224805945098</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>3.270000579611436</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>40.48698847399605</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>38.78143885933063</v>
       </c>
     </row>
   </sheetData>

--- a/Output/BRDM_countarea_ALM_A1_PLCigaretteButts.xlsx
+++ b/Output/BRDM_countarea_ALM_A1_PLCigaretteButts.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,6 +1789,374 @@
         <v>101.3333333333333</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>55.03875968992248</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13.18234610917538</v>
+      </c>
+      <c r="E8" t="n">
+        <v>564.0926801608481</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>103.0008091248401</v>
+      </c>
+      <c r="I8" t="n">
+        <v>17.71164944724882</v>
+      </c>
+      <c r="J8" t="n">
+        <v>56.60818713450292</v>
+      </c>
+      <c r="K8" t="n">
+        <v>232.0021705545064</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>52.91245791245791</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21.65926225860927</v>
+      </c>
+      <c r="O8" t="n">
+        <v>90.07239843728655</v>
+      </c>
+      <c r="P8" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>34.62596641856347</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.865854452955317</v>
+      </c>
+      <c r="T8" t="n">
+        <v>184.8763222681811</v>
+      </c>
+      <c r="U8" t="n">
+        <v>194.6666666666667</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>44.07831470128622</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18.02153567977759</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>303.9104237565315</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>208.3127061127255</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.965551650830838</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>34.99680389924293</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.875786163522013</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>251.5001673089117</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>294.2098183637905</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.696470555216865</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>27.8071411792342</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.83939300145986</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>226.7866741810864</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>142.816299842061</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>48.70709403119101</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>13.37073263332989</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>705.2340252895873</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>103.2944362831958</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>16.42996379838485</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>21.93085064056656</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.198067632850242</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>127.6483639669797</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>157.6769372123065</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.745082078415412</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>377.5250003962028</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>182.6981707317073</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.468846147235257</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>375.8270153618991</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>90.66666666666667</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>156.6852367688022</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.750804750804751</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>308.6324786324786</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>19.63665858363001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>154.6251993620415</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>21.60723268058469</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>396.8253968253968</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>133.3333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.64769647696477</v>
+      </c>
+      <c r="E9" t="n">
+        <v>369.7762439089281</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>75.09487641270587</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26.5206623029664</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.38596491228071</v>
+      </c>
+      <c r="K9" t="n">
+        <v>95.01082208475589</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>106.6329966329967</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14.56649426099053</v>
+      </c>
+      <c r="O9" t="n">
+        <v>114.3878917028659</v>
+      </c>
+      <c r="P9" t="n">
+        <v>34.66666666666666</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>66.0368860475411</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.617956087710184</v>
+      </c>
+      <c r="T9" t="n">
+        <v>61.63461624599216</v>
+      </c>
+      <c r="U9" t="n">
+        <v>64</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>36.04099050366631</v>
+      </c>
+      <c r="X9" t="n">
+        <v>29.07136080319805</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>378.4041295934967</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>375.4976029278418</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.176524547082924</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>42.80194828975317</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.998915636521363</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>323.0406099137103</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>103.1827561498567</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4.081990233375436</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>74.06708278801302</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>13.2993281772824</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>211.1728632729018</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>414.125478130162</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>18.5975103052685</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>15.34183251705515</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>684.1139723705469</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.137069110172281</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>23.39476406461367</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.657362004043927</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>98.75334490489622</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>29.33333333333334</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>215.9452722740753</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14.02619137210332</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>278.7207404237785</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>295.6357271906052</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>47.96902662472714</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>117.2771672771673</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>61.33333333333334</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>602.2945301521137</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>15.64549576177483</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>309.017094017094</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>170.6666666666667</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>49.94471026049974</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>7.627579162930748</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>323.8476800976801</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1800,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,6 +3529,374 @@
         <v>38.78143885933063</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>16.40776006861762</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.189333293095173</v>
+      </c>
+      <c r="E8" t="n">
+        <v>97.67948860659264</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.86548085423136</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>21.68784496179988</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.291530192027483</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.365639645495985</v>
+      </c>
+      <c r="K8" t="n">
+        <v>76.96423533567703</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>45.13923873409514</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.02985639654307</v>
+      </c>
+      <c r="O8" t="n">
+        <v>29.42449957964606</v>
+      </c>
+      <c r="P8" t="n">
+        <v>33.57247549870446</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>15.26820441243771</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.723914605656912</v>
+      </c>
+      <c r="T8" t="n">
+        <v>98.94461464699422</v>
+      </c>
+      <c r="U8" t="n">
+        <v>71.00547709703652</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6.684526701762532</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8.957790008730271</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>138.1862980759731</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>129.9373045246139</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.184540267913382</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>13.60586874246379</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.939210877607552</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>50.61853042873711</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>47.20254318311684</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.024699540760349</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.993503982733138</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.219623832389219</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>61.84582326252215</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>94.05497959818672</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>12.91884746180828</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.683814139242156</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>165.758953134178</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>40.12348750219154</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10.73480104004254</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.598248273549343</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.3903059353776</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>47.71649307458249</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.265986323710904</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>79.32597775370979</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.289893251474998</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>129.7895264375713</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>85.64490314222166</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.987964090440195</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>143.8992745497997</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>46.26493752772659</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>78.81806621852881</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.701968723388352</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>35.88771108608516</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>17.38453974720706</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>7.488150028100099</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>37.6093542969132</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>5.666521167053825</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>46.4534704475839</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>18.85618083164127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>24.42783140556392</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.657741929359846</v>
+      </c>
+      <c r="E9" t="n">
+        <v>101.3629377948764</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.62373051610846</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>17.56762970468337</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.19107817861384</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.389638554736632</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.94755775750529</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>94.46524435307285</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.109922916685266</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21.66929194588469</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.36482466066094</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>19.52717393449879</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.535451433210665</v>
+      </c>
+      <c r="T9" t="n">
+        <v>27.24601530456351</v>
+      </c>
+      <c r="U9" t="n">
+        <v>22.07059380966247</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.816496580927726</v>
+      </c>
+      <c r="W9" t="n">
+        <v>15.20580447374236</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.65333016603341</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>35.1425181200553</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>186.9759105641598</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.807946318286858</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16.89556837907969</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.647263682729357</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>35.98010978814367</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>16.4181886909272</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.123437481835682</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15.80800280658775</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>4.295162240704339</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>31.58750323800813</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>338.760946027792</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>3.973821362023534</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>7.823974030489412</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>204.5459112994421</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.315474722715388</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.724848078293002</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.331363569740981</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>34.18955919145597</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.7746025264604</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>102.5141475990637</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.860756022208454</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>36.31674809753912</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>127.8353583930307</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17.58010811323821</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>59.39737989736121</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>28.15828277592383</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>243.8617727910057</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.047411666029773</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>47.4578566251499</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>75.58953484297795</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>32.11455342957441</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>4.921851861013567</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>105.9657598173479</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>30.28751117760146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
